--- a/business_surveys/022_social_media_audit_form--business_surveys.xlsx
+++ b/business_surveys/022_social_media_audit_form--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>social_media_platforms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Header</t>
+          <t>Social Media Platform(s) Used</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,63 +538,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>social_media_platforms</t>
+          <t>current_posts</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>social_media_platforms</t>
+          <t>Current Posts</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>current_posts</t>
+          <t>engagement_rate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>current_posts</t>
+          <t>Engagement Rate</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>post_engagement</t>
+          <t>audience_demographics</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>post_engagement</t>
+          <t>Audience Demographics</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>post_engagement_percentage</t>
+          <t>audience_language</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>post_engagement_percentage</t>
+          <t>Audience Language</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,86 +630,86 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>audience_demographics</t>
+          <t>current_followers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>audience_demographics</t>
+          <t>Current Followers</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>audience_age_range</t>
+          <t>follower_growth_rate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>audience_age_range</t>
+          <t>Follower Growth Rate</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>audience_location</t>
+          <t>average_posts_per_month</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>audience_location</t>
+          <t>Average Posts per Month</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>audience_language</t>
+          <t>engagement_boosting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>audience_language</t>
+          <t>Engagement Boosting Strategy</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>current_followers</t>
+          <t>average_engagement_boosting_rate</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>current_followers</t>
+          <t>Average Engagement Boosting Rate</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>current_followers_growth</t>
+          <t>average_posts_growth_rate</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>current_followers_growth</t>
+          <t>Average Posts Growth Rate</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>current_posts_per_month</t>
+          <t>boosting_cost</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>current_posts_per_month</t>
+          <t>Boosting Cost</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,660 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>current_posts_per_month_growth</t>
+          <t>average_boosting_cost</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>current_posts_per_month_growth</t>
+          <t>Average Boosting Cost</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>followers_growth_rate</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>followers_growth_rate</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>engagement_rate</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>engagement_rate</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>engagement_rate_percentage</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>engagement_rate_percentage</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>follower_acquisition_cost</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>follower_acquisition_cost</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>average_engagement_rate</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>average_engagement_rate</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>engagement_cost</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>engagement_cost</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>engagement_boosting</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>engagement_boosting</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>average_followers_per_post</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>average_followers_per_post</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_rate</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_rate</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>average_engagement_cost</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>average_engagement_cost</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>average_posts</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>average_posts</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>average_posts_growth</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>average_posts_growth</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>average_boosting_rate</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>average_boosting_rate</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>boosting_cost</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>boosting_cost</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>average_followers_growth_rate</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>average_followers_growth_rate</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>boosting_rate</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>boosting_rate</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_rate</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_rate</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>follower_acquisition_cost</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>follower_acquisition_cost</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>average_boosting_cost</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>average_boosting_cost</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>engagement_boosting_growth</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>engagement_boosting_growth</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>boosting</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>boosting</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>average_engagement_boosting_cost</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>follower_acquisition_boosting_rate</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>follower_acquisition_boosting_rate</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>follower_acquisition_boosting_cost</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>follower_acquisition_boosting_cost</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>engagement_boosting_boosting</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>engagement_boosting_boosting</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1466,10 +822,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1567,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>18-24</t>
         </is>
       </c>
     </row>
@@ -1584,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>25-34</t>
         </is>
       </c>
     </row>
@@ -1601,350 +957,180 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>35-44</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_demographics_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>45-54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_demographics_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_demographics_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65_or_older</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65 or older</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_language_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>English</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_language_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>audience_age_range_choices</t>
+          <t>audience_language_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>65_or_older</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>65 or older</t>
+          <t>French</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>audience_location_choices</t>
+          <t>audience_language_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usa</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>audience_location_choices</t>
+          <t>engagement_boosting_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>canada</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>audience_location_choices</t>
+          <t>engagement_boosting_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>mexico</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>audience_location_choices</t>
+          <t>engagement_boosting_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>audience_language_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>english</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>English</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>audience_language_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>spanish</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Spanish</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>audience_language_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>french</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>French</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>audience_language_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>boosting_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>boosting_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>boosting_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>engagement_boosting_boosting_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>engagement_boosting_boosting_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>engagement_boosting_boosting_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
